--- a/weekly_message/0606_토2.xlsx
+++ b/weekly_message/0606_토2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\9191h\Desktop\[중1] - 1학기 진도 사항\TextMessage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\9191h\Desktop\[중1] - 1학기 진도 사항\weekly_message\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6019ECE8-2732-49E9-A3F6-E4600AF15258}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72504425-A819-48EB-B17F-C2138F5BC0A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -650,7 +650,7 @@
       <c r="L2" s="7"/>
       <c r="M2" s="7"/>
       <c r="N2" s="11" t="str">
-        <f t="shared" ref="N2:N8" si="1">"▷ "&amp;B2&amp;"는 이번 주간 테스트에서 "&amp;C2&amp;"점을 받았습니다."&amp;CHAR(10)&amp;
+        <f>"▷ "&amp;B2&amp;"는 이번 주간 테스트에서 "&amp;C2&amp;"점을 받았습니다."&amp;CHAR(10)&amp;CHAR(10)&amp;
 IF(C2=100,"",
 "- 독서 : "&amp;(5-N(D2)-N(E2))&amp;"/5"&amp;CHAR(10)&amp;
 "- 비문학 : "&amp;(4-N(F2))&amp;"/4"&amp;CHAR(10)&amp;
@@ -679,7 +679,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="114.75" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:17" ht="127.5" x14ac:dyDescent="0.35">
       <c r="B3" s="1" t="s">
         <v>8</v>
       </c>
@@ -698,7 +698,23 @@
       <c r="L3" s="7"/>
       <c r="M3" s="7"/>
       <c r="N3" s="11" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="N3:N11" si="1">"▷ "&amp;B3&amp;"는 이번 주간 테스트에서 "&amp;C3&amp;"점을 받았습니다."&amp;CHAR(10)&amp;CHAR(10)&amp;
+IF(C3=100,"",
+"- 독서 : "&amp;(5-N(D3)-N(E3))&amp;"/5"&amp;CHAR(10)&amp;
+"- 비문학 : "&amp;(4-N(F3))&amp;"/4"&amp;CHAR(10)&amp;
+"- 문학 : "&amp;(5-IF(G3="",0,LEN(SUBSTITUTE(G3," ",""))-LEN(SUBSTITUTE(SUBSTITUTE(G3," ",""),",",""))+1))&amp;"/5"&amp;CHAR(10)&amp;
+"- 문법 : "&amp;(4-IF(H3="",0,LEN(SUBSTITUTE(H3," ",""))-LEN(SUBSTITUTE(SUBSTITUTE(H3," ",""),",",""))+1))&amp;"/4"&amp;CHAR(10)&amp;
+"- 어휘 : "&amp;(11-IF(I3="",0,1)-N(J3))&amp;"/11"&amp;CHAR(10)
+)&amp;
+IF(AND(K3="",L3=""),
+CHAR(10)&amp;"▷ 과 제 : 우수"&amp;CHAR(10)&amp;CHAR(10)&amp;"▷ 수 업 : 우수"&amp;CHAR(10)&amp;CHAR(10)&amp;"※ 과제와 수업에 특이사항이 있으면 전달 드리겠습니다.",
+IF(AND(K3&lt;&gt;"",L3=""),
+CHAR(10)&amp;"▷ 과 제"&amp;CHAR(10)&amp;"- "&amp;K3&amp;CHAR(10)&amp;CHAR(10)&amp;"▷ 수 업 : 우수",
+IF(AND(K3="",L3&lt;&gt;""),
+CHAR(10)&amp;"▷ 과 제 : 우수"&amp;CHAR(10)&amp;CHAR(10)&amp;"▷ 수 업"&amp;CHAR(10)&amp;"- "&amp;L3,
+CHAR(10)&amp;"▷ 과 제"&amp;CHAR(10)&amp;"- "&amp;K3&amp;CHAR(10)&amp;CHAR(10)&amp;"▷ 수 업"&amp;CHAR(10)&amp;"- "&amp;L3
+)))&amp;
+IF(M3&lt;&gt;"",CHAR(10)&amp;CHAR(10)&amp;"※ "&amp;M3,"")</f>
         <v>▷ 근휘는 이번 주간 테스트에서 100점을 받았습니다.
 ▷ 과 제 : 우수
 ▷ 수 업 : 우수
@@ -711,7 +727,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="114.75" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:17" ht="127.5" x14ac:dyDescent="0.35">
       <c r="B4" s="1" t="s">
         <v>9</v>
       </c>
@@ -743,7 +759,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="114.75" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:17" ht="127.5" x14ac:dyDescent="0.35">
       <c r="B5" s="1" t="s">
         <v>10</v>
       </c>
@@ -775,7 +791,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="114.75" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:17" ht="127.5" x14ac:dyDescent="0.35">
       <c r="B6" s="1" t="s">
         <v>11</v>
       </c>
@@ -807,7 +823,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="114.75" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:17" ht="127.5" x14ac:dyDescent="0.35">
       <c r="B7" s="1" t="s">
         <v>12</v>
       </c>
@@ -839,7 +855,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="114.75" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:17" ht="127.5" x14ac:dyDescent="0.35">
       <c r="B8" s="1" t="s">
         <v>21</v>
       </c>
@@ -865,7 +881,7 @@
 ※ 과제와 수업에 특이사항이 있으면 전달 드리겠습니다.</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="114.75" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:17" ht="127.5" x14ac:dyDescent="0.35">
       <c r="B9" s="2"/>
       <c r="C9" s="6">
         <f t="shared" ref="C9:C11" si="2">100-N(D9)*5-N(E9)*4-N(F9)*4-IF(G9="",0,(LEN(SUBSTITUTE(G9," ",""))-LEN(SUBSTITUTE(SUBSTITUTE(G9," ",""),",",""))+1)*4)-IF(H9="",0,(LEN(SUBSTITUTE(H9," ",""))-LEN(SUBSTITUTE(SUBSTITUTE(H9," ",""),",",""))+1)*4)-IF(I9="",0,5)-N(J9)*2</f>
@@ -882,30 +898,14 @@
       <c r="L9" s="7"/>
       <c r="M9" s="7"/>
       <c r="N9" s="11" t="str">
-        <f t="shared" ref="N9:N11" si="3">"▷ "&amp;B9&amp;"는 이번 주간 테스트에서 "&amp;C9&amp;"점을 받았습니다."&amp;CHAR(10)&amp;
-IF(C9=100,"",
-"- 독서 : "&amp;(5-N(D9)-N(E9))&amp;"/5"&amp;CHAR(10)&amp;
-"- 비문학 : "&amp;(4-N(F9))&amp;"/4"&amp;CHAR(10)&amp;
-"- 문학 : "&amp;(5-IF(G9="",0,LEN(SUBSTITUTE(G9," ",""))-LEN(SUBSTITUTE(SUBSTITUTE(G9," ",""),",",""))+1))&amp;"/5"&amp;CHAR(10)&amp;
-"- 문법 : "&amp;(4-IF(H9="",0,LEN(SUBSTITUTE(H9," ",""))-LEN(SUBSTITUTE(SUBSTITUTE(H9," ",""),",",""))+1))&amp;"/4"&amp;CHAR(10)&amp;
-"- 어휘 : "&amp;(11-IF(I9="",0,1)-N(J9))&amp;"/11"&amp;CHAR(10)
-)&amp;
-IF(AND(K9="",L9=""),
-CHAR(10)&amp;"▷ 과 제 : 우수"&amp;CHAR(10)&amp;CHAR(10)&amp;"▷ 수 업 : 우수"&amp;CHAR(10)&amp;CHAR(10)&amp;"※ 과제와 수업에 특이사항이 있으면 전달 드리겠습니다.",
-IF(AND(K9&lt;&gt;"",L9=""),
-CHAR(10)&amp;"▷ 과 제"&amp;CHAR(10)&amp;"- "&amp;K9&amp;CHAR(10)&amp;CHAR(10)&amp;"▷ 수 업 : 우수",
-IF(AND(K9="",L9&lt;&gt;""),
-CHAR(10)&amp;"▷ 과 제 : 우수"&amp;CHAR(10)&amp;CHAR(10)&amp;"▷ 수 업"&amp;CHAR(10)&amp;"- "&amp;L9,
-CHAR(10)&amp;"▷ 과 제"&amp;CHAR(10)&amp;"- "&amp;K9&amp;CHAR(10)&amp;CHAR(10)&amp;"▷ 수 업"&amp;CHAR(10)&amp;"- "&amp;L9
-)))&amp;
-IF(M9&lt;&gt;"",CHAR(10)&amp;CHAR(10)&amp;"※ "&amp;M9,"")</f>
+        <f t="shared" si="1"/>
         <v>▷ 는 이번 주간 테스트에서 100점을 받았습니다.
 ▷ 과 제 : 우수
 ▷ 수 업 : 우수
 ※ 과제와 수업에 특이사항이 있으면 전달 드리겠습니다.</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="114.75" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:17" ht="127.5" x14ac:dyDescent="0.35">
       <c r="B10" s="2"/>
       <c r="C10" s="6">
         <f t="shared" si="2"/>
@@ -922,14 +922,14 @@
       <c r="L10" s="7"/>
       <c r="M10" s="7"/>
       <c r="N10" s="11" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>▷ 는 이번 주간 테스트에서 100점을 받았습니다.
 ▷ 과 제 : 우수
 ▷ 수 업 : 우수
 ※ 과제와 수업에 특이사항이 있으면 전달 드리겠습니다.</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="114.75" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:17" ht="127.5" x14ac:dyDescent="0.35">
       <c r="B11" s="2"/>
       <c r="C11" s="6">
         <f t="shared" si="2"/>
@@ -946,7 +946,7 @@
       <c r="L11" s="7"/>
       <c r="M11" s="7"/>
       <c r="N11" s="11" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>▷ 는 이번 주간 테스트에서 100점을 받았습니다.
 ▷ 과 제 : 우수
 ▷ 수 업 : 우수

--- a/weekly_message/0606_토2.xlsx
+++ b/weekly_message/0606_토2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\9191h\Desktop\[중1] - 1학기 진도 사항\weekly_message\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72504425-A819-48EB-B17F-C2138F5BC0A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC37CE7F-C9AB-4E86-93F2-A98C376C7623}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="22">
   <si>
     <t>주테
 점수</t>
@@ -42,111 +42,87 @@
     <t>비문학</t>
   </si>
   <si>
+    <t>과제</t>
+  </si>
+  <si>
+    <t>수업</t>
+  </si>
+  <si>
+    <t>전달 사항</t>
+  </si>
+  <si>
+    <t>근휘</t>
+  </si>
+  <si>
+    <t>윤수</t>
+  </si>
+  <si>
+    <t>준서</t>
+  </si>
+  <si>
+    <t>우철이</t>
+  </si>
+  <si>
+    <t>이름</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>최종문자</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>날짜</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>가온이</t>
+  </si>
+  <si>
+    <t>솔한이</t>
+  </si>
+  <si>
+    <t>독서1~3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>독서4~6</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>문학</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>19번</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>20번</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>문법</t>
-  </si>
-  <si>
-    <t>어휘</t>
-  </si>
-  <si>
-    <t>과제</t>
-  </si>
-  <si>
-    <t>수업</t>
-  </si>
-  <si>
-    <t>전달 사항</t>
-  </si>
-  <si>
-    <t>근휘</t>
-  </si>
-  <si>
-    <t>윤수</t>
-  </si>
-  <si>
-    <t>승우</t>
-  </si>
-  <si>
-    <t>준서</t>
-  </si>
-  <si>
-    <t>우철이</t>
-  </si>
-  <si>
-    <t>독서 1~3</t>
-  </si>
-  <si>
-    <t>독서 4~5</t>
-  </si>
-  <si>
-    <t>문항수</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>이름</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>항목</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>최종문자</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>날짜</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>가온이</t>
-  </si>
-  <si>
-    <t>솔한이</t>
-  </si>
-  <si>
-    <t>독서1~3</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>독서4~6</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>문학</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>19번</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>20번</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>문법</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>다현이</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1월부터 시작된 학기가 어느덧 마지막을 향해 가고 있습니다. 아이들이 과제 수행에는 많이 익숙해졌지만, 최근에는 문제를 꼼꼼하게 확인하기보다 피상적으로 해결하려는 모습이 자주 보이고 있습니다.
+날씨가 점점 더워지면서 체력적으로 쉽게 지칠 수 있는 시기이지만, 과제를 수행할 때만큼은 조금 더 집중해서 끝까지 꼼꼼하게 확인하는 습관을 유지할 수 있도록 가정에서도 많은 격려 부탁드립니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -201,8 +177,31 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -247,13 +246,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
         <bgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
@@ -285,60 +302,79 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -556,100 +592,103 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AA2E436-B2B5-49B7-AFB8-CC247CCA8E17}">
-  <dimension ref="A1:Q11"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:Q10"/>
+  <sheetFormatPr defaultColWidth="7.59765625" defaultRowHeight="13.15" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.46484375" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.265625" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.1328125" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.46484375" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.265625" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.59765625" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.19921875" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.06640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23.9296875" style="3" customWidth="1"/>
-    <col min="12" max="12" width="19.6640625" style="3" customWidth="1"/>
-    <col min="13" max="13" width="33.46484375" style="3" customWidth="1"/>
-    <col min="14" max="14" width="39.265625" style="12" customWidth="1"/>
-    <col min="15" max="16" width="8.265625" style="3" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="6.46484375" style="3" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.06640625" style="3"/>
+    <col min="1" max="1" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.46484375" style="19" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.265625" style="19" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="8.06640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.06640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.6640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="15.1328125" style="1" customWidth="1"/>
+    <col min="9" max="10" width="5.06640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.06640625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="15.3984375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="42.73046875" style="22" customWidth="1"/>
+    <col min="14" max="14" width="50.6640625" style="23" customWidth="1"/>
+    <col min="15" max="15" width="7.59765625" style="1"/>
+    <col min="16" max="17" width="7.59765625" style="24"/>
+    <col min="18" max="16384" width="7.59765625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:14" ht="15.75" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="I1" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="M1" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="N1" s="21" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="293.25" x14ac:dyDescent="0.35">
+      <c r="A2" s="25">
+        <f ca="1">TODAY()</f>
+        <v>46179</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="16">
+        <f t="shared" ref="C2:C7" si="0">100-N(D2)*5-N(E2)*4-N(F2)*4-IF(G2="",0,(LEN(SUBSTITUTE(G2," ",""))-LEN(SUBSTITUTE(SUBSTITUTE(G2," ",""),",",""))+1)*4)-IF(H2="",0,(LEN(SUBSTITUTE(H2," ",""))-LEN(SUBSTITUTE(SUBSTITUTE(H2," ",""),",",""))+1)*4)-IF(I2="",0,5)-N(J2)*2</f>
+        <v>83</v>
+      </c>
+      <c r="D2" s="7">
+        <v>1</v>
+      </c>
+      <c r="E2" s="8"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="11">
+        <v>10</v>
+      </c>
+      <c r="H2" s="12">
         <v>16</v>
       </c>
-      <c r="C1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="K1" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="L1" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="M1" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="N1" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="P1" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q1" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" ht="114.75" x14ac:dyDescent="0.35">
-      <c r="A2" s="4">
-        <v>46171</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" s="6">
-        <f t="shared" ref="C2:C8" si="0">100-N(D2)*5-N(E2)*4-N(F2)*4-IF(G2="",0,(LEN(SUBSTITUTE(G2," ",""))-LEN(SUBSTITUTE(SUBSTITUTE(G2," ",""),",",""))+1)*4)-IF(H2="",0,(LEN(SUBSTITUTE(H2," ",""))-LEN(SUBSTITUTE(SUBSTITUTE(H2," ",""),",",""))+1)*4)-IF(I2="",0,5)-N(J2)*2</f>
-        <v>100</v>
-      </c>
-      <c r="D2" s="14"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="11" t="str">
+      <c r="I2" s="10"/>
+      <c r="J2" s="13">
+        <v>2</v>
+      </c>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="N2" s="6" t="str">
         <f>"▷ "&amp;B2&amp;"는 이번 주간 테스트에서 "&amp;C2&amp;"점을 받았습니다."&amp;CHAR(10)&amp;CHAR(10)&amp;
 IF(C2=100,"",
 "- 독서 : "&amp;(5-N(D2)-N(E2))&amp;"/5"&amp;CHAR(10)&amp;
@@ -667,38 +706,47 @@
 CHAR(10)&amp;"▷ 과 제"&amp;CHAR(10)&amp;"- "&amp;K2&amp;CHAR(10)&amp;CHAR(10)&amp;"▷ 수 업"&amp;CHAR(10)&amp;"- "&amp;L2
 )))&amp;
 IF(M2&lt;&gt;"",CHAR(10)&amp;CHAR(10)&amp;"※ "&amp;M2,"")</f>
-        <v>▷ 가온이는 이번 주간 테스트에서 100점을 받았습니다.
+        <v>▷ 가온이는 이번 주간 테스트에서 83점을 받았습니다.
+- 독서 : 4/5
+- 비문학 : 4/4
+- 문학 : 4/5
+- 문법 : 3/4
+- 어휘 : 9/11
 ▷ 과 제 : 우수
 ▷ 수 업 : 우수
-※ 과제와 수업에 특이사항이 있으면 전달 드리겠습니다.</v>
-      </c>
-      <c r="P2" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q2" s="10">
-        <v>3</v>
+※ 과제와 수업에 특이사항이 있으면 전달 드리겠습니다.
+※ 1월부터 시작된 학기가 어느덧 마지막을 향해 가고 있습니다. 아이들이 과제 수행에는 많이 익숙해졌지만, 최근에는 문제를 꼼꼼하게 확인하기보다 피상적으로 해결하려는 모습이 자주 보이고 있습니다.
+날씨가 점점 더워지면서 체력적으로 쉽게 지칠 수 있는 시기이지만, 과제를 수행할 때만큼은 조금 더 집중해서 끝까지 꼼꼼하게 확인하는 습관을 유지할 수 있도록 가정에서도 많은 격려 부탁드립니다.</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="127.5" x14ac:dyDescent="0.35">
-      <c r="B3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="6">
+    <row r="3" spans="1:14" ht="293.25" x14ac:dyDescent="0.35">
+      <c r="A3" s="25">
+        <f t="shared" ref="A3:A10" ca="1" si="1">TODAY()</f>
+        <v>46179</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="16">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="D3" s="14"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="17"/>
-      <c r="H3" s="17"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="15"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
-      <c r="M3" s="7"/>
-      <c r="N3" s="11" t="str">
-        <f t="shared" ref="N3:N11" si="1">"▷ "&amp;B3&amp;"는 이번 주간 테스트에서 "&amp;C3&amp;"점을 받았습니다."&amp;CHAR(10)&amp;CHAR(10)&amp;
+        <v>90</v>
+      </c>
+      <c r="D3" s="7">
+        <v>2</v>
+      </c>
+      <c r="E3" s="8"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="N3" s="6" t="str">
+        <f t="shared" ref="N3:N10" si="2">"▷ "&amp;B3&amp;"는 이번 주간 테스트에서 "&amp;C3&amp;"점을 받았습니다."&amp;CHAR(10)&amp;CHAR(10)&amp;
 IF(C3=100,"",
 "- 독서 : "&amp;(5-N(D3)-N(E3))&amp;"/5"&amp;CHAR(10)&amp;
 "- 비문학 : "&amp;(4-N(F3))&amp;"/4"&amp;CHAR(10)&amp;
@@ -715,246 +763,292 @@
 CHAR(10)&amp;"▷ 과 제"&amp;CHAR(10)&amp;"- "&amp;K3&amp;CHAR(10)&amp;CHAR(10)&amp;"▷ 수 업"&amp;CHAR(10)&amp;"- "&amp;L3
 )))&amp;
 IF(M3&lt;&gt;"",CHAR(10)&amp;CHAR(10)&amp;"※ "&amp;M3,"")</f>
-        <v>▷ 근휘는 이번 주간 테스트에서 100점을 받았습니다.
+        <v>▷ 근휘는 이번 주간 테스트에서 90점을 받았습니다.
+- 독서 : 3/5
+- 비문학 : 4/4
+- 문학 : 5/5
+- 문법 : 4/4
+- 어휘 : 11/11
 ▷ 과 제 : 우수
 ▷ 수 업 : 우수
-※ 과제와 수업에 특이사항이 있으면 전달 드리겠습니다.</v>
-      </c>
-      <c r="P3" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q3" s="10">
-        <v>3</v>
+※ 과제와 수업에 특이사항이 있으면 전달 드리겠습니다.
+※ 1월부터 시작된 학기가 어느덧 마지막을 향해 가고 있습니다. 아이들이 과제 수행에는 많이 익숙해졌지만, 최근에는 문제를 꼼꼼하게 확인하기보다 피상적으로 해결하려는 모습이 자주 보이고 있습니다.
+날씨가 점점 더워지면서 체력적으로 쉽게 지칠 수 있는 시기이지만, 과제를 수행할 때만큼은 조금 더 집중해서 끝까지 꼼꼼하게 확인하는 습관을 유지할 수 있도록 가정에서도 많은 격려 부탁드립니다.</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="127.5" x14ac:dyDescent="0.35">
-      <c r="B4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="6">
+    <row r="4" spans="1:14" ht="293.25" x14ac:dyDescent="0.35">
+      <c r="A4" s="25">
+        <f t="shared" ca="1" si="1"/>
+        <v>46179</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="16">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="D4" s="14"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="15"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
-      <c r="M4" s="7"/>
-      <c r="N4" s="11" t="str">
-        <f t="shared" si="1"/>
-        <v>▷ 윤수는 이번 주간 테스트에서 100점을 받았습니다.
+        <v>96</v>
+      </c>
+      <c r="D4" s="7"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="12">
+        <v>17</v>
+      </c>
+      <c r="I4" s="10"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="N4" s="6" t="str">
+        <f t="shared" si="2"/>
+        <v>▷ 윤수는 이번 주간 테스트에서 96점을 받았습니다.
+- 독서 : 5/5
+- 비문학 : 4/4
+- 문학 : 5/5
+- 문법 : 3/4
+- 어휘 : 11/11
 ▷ 과 제 : 우수
 ▷ 수 업 : 우수
-※ 과제와 수업에 특이사항이 있으면 전달 드리겠습니다.</v>
-      </c>
-      <c r="P4" s="10" t="s">
+※ 과제와 수업에 특이사항이 있으면 전달 드리겠습니다.
+※ 1월부터 시작된 학기가 어느덧 마지막을 향해 가고 있습니다. 아이들이 과제 수행에는 많이 익숙해졌지만, 최근에는 문제를 꼼꼼하게 확인하기보다 피상적으로 해결하려는 모습이 자주 보이고 있습니다.
+날씨가 점점 더워지면서 체력적으로 쉽게 지칠 수 있는 시기이지만, 과제를 수행할 때만큼은 조금 더 집중해서 끝까지 꼼꼼하게 확인하는 습관을 유지할 수 있도록 가정에서도 많은 격려 부탁드립니다.</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="293.25" x14ac:dyDescent="0.35">
+      <c r="A5" s="25">
+        <f t="shared" ca="1" si="1"/>
+        <v>46179</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="16">
+        <f t="shared" si="0"/>
+        <v>95</v>
+      </c>
+      <c r="D5" s="7">
         <v>1</v>
       </c>
-      <c r="Q4" s="10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" ht="127.5" x14ac:dyDescent="0.35">
-      <c r="B5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="6">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="D5" s="14"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="17"/>
-      <c r="H5" s="17"/>
-      <c r="I5" s="18"/>
-      <c r="J5" s="15"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="7"/>
-      <c r="M5" s="7"/>
-      <c r="N5" s="11" t="str">
-        <f t="shared" si="1"/>
-        <v>▷ 승우는 이번 주간 테스트에서 100점을 받았습니다.
+      <c r="E5" s="8"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="N5" s="6" t="str">
+        <f t="shared" si="2"/>
+        <v>▷ 준서는 이번 주간 테스트에서 95점을 받았습니다.
+- 독서 : 4/5
+- 비문학 : 4/4
+- 문학 : 5/5
+- 문법 : 4/4
+- 어휘 : 11/11
 ▷ 과 제 : 우수
 ▷ 수 업 : 우수
-※ 과제와 수업에 특이사항이 있으면 전달 드리겠습니다.</v>
-      </c>
-      <c r="P5" s="10" t="s">
+※ 과제와 수업에 특이사항이 있으면 전달 드리겠습니다.
+※ 1월부터 시작된 학기가 어느덧 마지막을 향해 가고 있습니다. 아이들이 과제 수행에는 많이 익숙해졌지만, 최근에는 문제를 꼼꼼하게 확인하기보다 피상적으로 해결하려는 모습이 자주 보이고 있습니다.
+날씨가 점점 더워지면서 체력적으로 쉽게 지칠 수 있는 시기이지만, 과제를 수행할 때만큼은 조금 더 집중해서 끝까지 꼼꼼하게 확인하는 습관을 유지할 수 있도록 가정에서도 많은 격려 부탁드립니다.</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="293.25" x14ac:dyDescent="0.35">
+      <c r="A6" s="25">
+        <f t="shared" ca="1" si="1"/>
+        <v>46179</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="16">
+        <f t="shared" si="0"/>
+        <v>83</v>
+      </c>
+      <c r="D6" s="7">
+        <v>1</v>
+      </c>
+      <c r="E6" s="8"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="11">
+        <v>10</v>
+      </c>
+      <c r="H6" s="12">
+        <v>18</v>
+      </c>
+      <c r="I6" s="10"/>
+      <c r="J6" s="13">
         <v>2</v>
       </c>
-      <c r="Q5" s="10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" ht="127.5" x14ac:dyDescent="0.35">
-      <c r="B6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="6">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="D6" s="14"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="17"/>
-      <c r="I6" s="18"/>
-      <c r="J6" s="15"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
-      <c r="N6" s="11" t="str">
-        <f t="shared" si="1"/>
-        <v>▷ 준서는 이번 주간 테스트에서 100점을 받았습니다.
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="N6" s="6" t="str">
+        <f t="shared" si="2"/>
+        <v>▷ 우철이는 이번 주간 테스트에서 83점을 받았습니다.
+- 독서 : 4/5
+- 비문학 : 4/4
+- 문학 : 4/5
+- 문법 : 3/4
+- 어휘 : 9/11
 ▷ 과 제 : 우수
 ▷ 수 업 : 우수
-※ 과제와 수업에 특이사항이 있으면 전달 드리겠습니다.</v>
-      </c>
-      <c r="P6" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q6" s="10">
-        <v>4</v>
+※ 과제와 수업에 특이사항이 있으면 전달 드리겠습니다.
+※ 1월부터 시작된 학기가 어느덧 마지막을 향해 가고 있습니다. 아이들이 과제 수행에는 많이 익숙해졌지만, 최근에는 문제를 꼼꼼하게 확인하기보다 피상적으로 해결하려는 모습이 자주 보이고 있습니다.
+날씨가 점점 더워지면서 체력적으로 쉽게 지칠 수 있는 시기이지만, 과제를 수행할 때만큼은 조금 더 집중해서 끝까지 꼼꼼하게 확인하는 습관을 유지할 수 있도록 가정에서도 많은 격려 부탁드립니다.</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="127.5" x14ac:dyDescent="0.35">
-      <c r="B7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="6">
+    <row r="7" spans="1:14" ht="293.25" x14ac:dyDescent="0.35">
+      <c r="A7" s="25">
+        <f t="shared" ca="1" si="1"/>
+        <v>46179</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="16">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="D7" s="14"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="17"/>
-      <c r="H7" s="17"/>
-      <c r="I7" s="18"/>
-      <c r="J7" s="15"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-      <c r="N7" s="11" t="str">
-        <f t="shared" si="1"/>
-        <v>▷ 우철이는 이번 주간 테스트에서 100점을 받았습니다.
+        <v>87</v>
+      </c>
+      <c r="D7" s="7"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="11">
+        <v>10</v>
+      </c>
+      <c r="H7" s="12">
+        <v>18</v>
+      </c>
+      <c r="I7" s="10">
+        <v>1</v>
+      </c>
+      <c r="J7" s="13"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="N7" s="6" t="str">
+        <f t="shared" si="2"/>
+        <v>▷ 솔한이는 이번 주간 테스트에서 87점을 받았습니다.
+- 독서 : 5/5
+- 비문학 : 4/4
+- 문학 : 4/5
+- 문법 : 3/4
+- 어휘 : 10/11
 ▷ 과 제 : 우수
 ▷ 수 업 : 우수
-※ 과제와 수업에 특이사항이 있으면 전달 드리겠습니다.</v>
-      </c>
-      <c r="P7" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q7" s="10">
-        <v>11</v>
+※ 과제와 수업에 특이사항이 있으면 전달 드리겠습니다.
+※ 1월부터 시작된 학기가 어느덧 마지막을 향해 가고 있습니다. 아이들이 과제 수행에는 많이 익숙해졌지만, 최근에는 문제를 꼼꼼하게 확인하기보다 피상적으로 해결하려는 모습이 자주 보이고 있습니다.
+날씨가 점점 더워지면서 체력적으로 쉽게 지칠 수 있는 시기이지만, 과제를 수행할 때만큼은 조금 더 집중해서 끝까지 꼼꼼하게 확인하는 습관을 유지할 수 있도록 가정에서도 많은 격려 부탁드립니다.</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="127.5" x14ac:dyDescent="0.35">
-      <c r="B8" s="1" t="s">
+    <row r="8" spans="1:14" ht="293.25" x14ac:dyDescent="0.35">
+      <c r="A8" s="25">
+        <f t="shared" ca="1" si="1"/>
+        <v>46179</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="16">
+        <f t="shared" ref="C8:C10" si="3">100-N(D8)*5-N(E8)*4-N(F8)*4-IF(G8="",0,(LEN(SUBSTITUTE(G8," ",""))-LEN(SUBSTITUTE(SUBSTITUTE(G8," ",""),",",""))+1)*4)-IF(H8="",0,(LEN(SUBSTITUTE(H8," ",""))-LEN(SUBSTITUTE(SUBSTITUTE(H8," ",""),",",""))+1)*4)-IF(I8="",0,5)-N(J8)*2</f>
+        <v>95</v>
+      </c>
+      <c r="D8" s="7">
+        <v>1</v>
+      </c>
+      <c r="E8" s="8"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="10"/>
+      <c r="J8" s="13"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="6">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="D8" s="14"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="17"/>
-      <c r="I8" s="18"/>
-      <c r="J8" s="15"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="7"/>
-      <c r="N8" s="11" t="str">
-        <f t="shared" si="1"/>
-        <v>▷ 솔한이는 이번 주간 테스트에서 100점을 받았습니다.
+      <c r="N8" s="6" t="str">
+        <f t="shared" si="2"/>
+        <v>▷ 다현이는 이번 주간 테스트에서 95점을 받았습니다.
+- 독서 : 4/5
+- 비문학 : 4/4
+- 문학 : 5/5
+- 문법 : 4/4
+- 어휘 : 11/11
 ▷ 과 제 : 우수
 ▷ 수 업 : 우수
-※ 과제와 수업에 특이사항이 있으면 전달 드리겠습니다.</v>
+※ 과제와 수업에 특이사항이 있으면 전달 드리겠습니다.
+※ 1월부터 시작된 학기가 어느덧 마지막을 향해 가고 있습니다. 아이들이 과제 수행에는 많이 익숙해졌지만, 최근에는 문제를 꼼꼼하게 확인하기보다 피상적으로 해결하려는 모습이 자주 보이고 있습니다.
+날씨가 점점 더워지면서 체력적으로 쉽게 지칠 수 있는 시기이지만, 과제를 수행할 때만큼은 조금 더 집중해서 끝까지 꼼꼼하게 확인하는 습관을 유지할 수 있도록 가정에서도 많은 격려 부탁드립니다.</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="127.5" x14ac:dyDescent="0.35">
-      <c r="B9" s="2"/>
-      <c r="C9" s="6">
-        <f t="shared" ref="C9:C11" si="2">100-N(D9)*5-N(E9)*4-N(F9)*4-IF(G9="",0,(LEN(SUBSTITUTE(G9," ",""))-LEN(SUBSTITUTE(SUBSTITUTE(G9," ",""),",",""))+1)*4)-IF(H9="",0,(LEN(SUBSTITUTE(H9," ",""))-LEN(SUBSTITUTE(SUBSTITUTE(H9," ",""),",",""))+1)*4)-IF(I9="",0,5)-N(J9)*2</f>
+    <row r="9" spans="1:14" ht="102" x14ac:dyDescent="0.35">
+      <c r="A9" s="25">
+        <f t="shared" ca="1" si="1"/>
+        <v>46179</v>
+      </c>
+      <c r="B9" s="18"/>
+      <c r="C9" s="16">
+        <f t="shared" si="3"/>
         <v>100</v>
       </c>
-      <c r="D9" s="14"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="17"/>
-      <c r="H9" s="17"/>
-      <c r="I9" s="18"/>
-      <c r="J9" s="15"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="7"/>
-      <c r="M9" s="7"/>
-      <c r="N9" s="11" t="str">
-        <f t="shared" si="1"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="12"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="13"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="14"/>
+      <c r="N9" s="6" t="str">
+        <f t="shared" si="2"/>
         <v>▷ 는 이번 주간 테스트에서 100점을 받았습니다.
 ▷ 과 제 : 우수
 ▷ 수 업 : 우수
 ※ 과제와 수업에 특이사항이 있으면 전달 드리겠습니다.</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="127.5" x14ac:dyDescent="0.35">
-      <c r="B10" s="2"/>
-      <c r="C10" s="6">
+    <row r="10" spans="1:14" ht="102" x14ac:dyDescent="0.35">
+      <c r="A10" s="25">
+        <f t="shared" ca="1" si="1"/>
+        <v>46179</v>
+      </c>
+      <c r="B10" s="18"/>
+      <c r="C10" s="16">
+        <f t="shared" si="3"/>
+        <v>100</v>
+      </c>
+      <c r="D10" s="7"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="12"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="14"/>
+      <c r="N10" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>100</v>
-      </c>
-      <c r="D10" s="14"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="17"/>
-      <c r="I10" s="18"/>
-      <c r="J10" s="15"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="7"/>
-      <c r="M10" s="7"/>
-      <c r="N10" s="11" t="str">
-        <f t="shared" si="1"/>
         <v>▷ 는 이번 주간 테스트에서 100점을 받았습니다.
 ▷ 과 제 : 우수
 ▷ 수 업 : 우수
 ※ 과제와 수업에 특이사항이 있으면 전달 드리겠습니다.</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="127.5" x14ac:dyDescent="0.35">
-      <c r="B11" s="2"/>
-      <c r="C11" s="6">
-        <f t="shared" si="2"/>
-        <v>100</v>
-      </c>
-      <c r="D11" s="14"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="17"/>
-      <c r="I11" s="18"/>
-      <c r="J11" s="15"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="7"/>
-      <c r="M11" s="7"/>
-      <c r="N11" s="11" t="str">
-        <f t="shared" si="1"/>
-        <v>▷ 는 이번 주간 테스트에서 100점을 받았습니다.
-▷ 과 제 : 우수
-▷ 수 업 : 우수
-※ 과제와 수업에 특이사항이 있으면 전달 드리겠습니다.</v>
-      </c>
-    </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>